--- a/src/main/webapp/WEB-INF/jsp/egovframework/com/uss/ion/bnt/example/excelBNDT.xlsx
+++ b/src/main/webapp/WEB-INF/jsp/egovframework/com/uss/ion/bnt/example/excelBNDT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\eGovFrameDev-4.0.0-64bit\workspace\egovframework-all-in-one-AllNew\src\main\webapp\WEB-INF\jsp\egovframework\com\uss\ion\bnt\example\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/EGOV2026/eGovFrameDev-4.3.1/workspace-5.0.0/egovframework-all-in-one-AllNew-job/src/main/webapp/WEB-INF/jsp/egovframework/com/uss/ion/bnt/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95AB45B8-7746-407F-B0FE-3EF333873FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CDA7725-0A82-CA4F-B250-10E092A42A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="14505" windowWidth="15345" windowHeight="13170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5060" yWindow="4260" windowWidth="15340" windowHeight="13180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="17">
   <si>
     <t>당직일자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -42,42 +42,49 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>20220103</t>
+    <t>20260111</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>20220104</t>
-  </si>
-  <si>
-    <t>20220105</t>
-  </si>
-  <si>
-    <t>20220106</t>
-  </si>
-  <si>
-    <t>20220107</t>
-  </si>
-  <si>
-    <t>20220108</t>
-  </si>
-  <si>
-    <t>20220109</t>
-  </si>
-  <si>
-    <t>20220110</t>
-  </si>
-  <si>
-    <t>20220111</t>
-  </si>
-  <si>
-    <t>20220112</t>
+    <t>20260112</t>
+  </si>
+  <si>
+    <t>20260113</t>
+  </si>
+  <si>
+    <t>20260114</t>
+  </si>
+  <si>
+    <t>20260115</t>
+  </si>
+  <si>
+    <t>20260116</t>
+  </si>
+  <si>
+    <t>20260117</t>
+  </si>
+  <si>
+    <t>20260118</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20260119</t>
+  </si>
+  <si>
+    <t>USRCNFRM_00000000000</t>
+  </si>
+  <si>
+    <t>TEST1</t>
+  </si>
+  <si>
+    <t>20260120</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <name val="돋움"/>
@@ -472,14 +479,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="51.5546875" customWidth="1"/>
+    <col min="2" max="2" width="51.5" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -490,7 +497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -501,7 +508,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -512,7 +519,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -523,7 +530,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -534,7 +541,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -545,7 +552,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -556,7 +563,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -567,7 +574,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -578,26 +585,26 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="C11" s="1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
